--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484147_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484147_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9434</v>
+        <v>3.7495</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6276</v>
+        <v>3.3215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3158</v>
+        <v>0.428</v>
       </c>
       <c r="G2" t="n">
         <v>1.5904</v>
@@ -610,13 +610,13 @@
         <v>0.9919</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4206</v>
+        <v>0.2267</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3798</v>
+        <v>0.0737</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0408</v>
+        <v>0.153</v>
       </c>
       <c r="V2" t="n">
         <v>0.9405</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4562</v>
+        <v>3.2801</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9491</v>
+        <v>1.7451</v>
       </c>
       <c r="F3" t="n">
-        <v>1.507</v>
+        <v>1.5351</v>
       </c>
       <c r="G3" t="n">
         <v>1.635</v>
@@ -688,13 +688,13 @@
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9483</v>
+        <v>0.7723</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3175</v>
+        <v>0.1134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6308</v>
+        <v>0.6589</v>
       </c>
       <c r="V3" t="n">
         <v>0.6745</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7008</v>
+        <v>2.6723</v>
       </c>
       <c r="E4" t="n">
-        <v>3.779</v>
+        <v>4.4139</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0782</v>
+        <v>-1.7415</v>
       </c>
       <c r="G4" t="n">
         <v>2.1221</v>
@@ -766,13 +766,13 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4646</v>
+        <v>-0.4931</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5894</v>
+        <v>0.0454</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8752</v>
+        <v>-0.5386</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9405</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,75 +799,71 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2918</v>
+        <v>0.6119</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0422</v>
+        <v>1.5595</v>
       </c>
       <c r="F5" t="n">
-        <v>0.334</v>
+        <v>-0.9476</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5896</v>
+        <v>0.8066</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8616</v>
+        <v>-1.094</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2721</v>
+        <v>1.9006</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.66</v>
+        <v>2.5344</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.66</v>
+        <v>1.0484</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.486</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07049999999999999</v>
+        <v>-1.7278</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2016</v>
+        <v>-2.1424</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2721</v>
+        <v>0.4146</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5442</v>
+        <v>-0.4563</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6178</v>
+        <v>0.0171</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0737</v>
+        <v>-0.4733</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3373</v>
+        <v>-0.532</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3373</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E. MAÑES CARRETERO</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -877,73 +873,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2355</v>
+        <v>0.4725</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3341</v>
+        <v>0.4608</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5696</v>
+        <v>0.0117</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0283</v>
+        <v>-1.867</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8116</v>
+        <v>-2.0316</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.8399</v>
+        <v>0.1646</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5937</v>
+        <v>0.5231</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0066</v>
+        <v>0.2419</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.6003</v>
+        <v>0.2811</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4346</v>
+        <v>-2.3901</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.195</v>
+        <v>-2.2736</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2396</v>
+        <v>-0.1165</v>
       </c>
       <c r="P6" t="n">
+        <v>2.3806</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.1984</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-2.1822</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>2.579</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7877</v>
+        <v>-0.0411</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5726</v>
+        <v>0.1361</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2151</v>
+        <v>-0.1772</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +951,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1441</v>
+        <v>0.4725</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1935</v>
+        <v>0.4608</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0494</v>
+        <v>0.0117</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.014</v>
+        <v>-1.867</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4283</v>
+        <v>-2.0316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5857</v>
+        <v>0.1646</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6353</v>
+        <v>0.5231</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1124</v>
+        <v>0.2419</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7478</v>
+        <v>0.2811</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3787</v>
+        <v>-2.3901</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.5408</v>
+        <v>-2.2736</v>
       </c>
       <c r="O7" t="n">
-        <v>0.162</v>
+        <v>-0.1165</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>2.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8338</v>
+        <v>-0.0411</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8501</v>
+        <v>0.1361</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0163</v>
+        <v>-0.1772</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1029,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0751</v>
+        <v>0.4181</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1911</v>
+        <v>1.6639</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.116</v>
+        <v>-1.2458</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8066</v>
+        <v>-3.014</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.094</v>
+        <v>-2.4283</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9006</v>
+        <v>-0.5857</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5344</v>
+        <v>-0.6353</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0484</v>
+        <v>0.1124</v>
       </c>
       <c r="L8" t="n">
-        <v>1.486</v>
+        <v>-0.7478</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7278</v>
+        <v>-2.3787</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1424</v>
+        <v>-2.5408</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4146</v>
+        <v>0.162</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7935</v>
+        <v>2.1822</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7855</v>
+        <v>2.1822</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.993</v>
+        <v>-0.5597</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3514</v>
+        <v>-0.3797</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6417</v>
+        <v>-0.1801</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.532</v>
+        <v>1.8097</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.532</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,71 +1107,75 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2545</v>
+        <v>-0.1163</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6945</v>
+        <v>-0.4503</v>
       </c>
       <c r="F9" t="n">
-        <v>0.44</v>
+        <v>0.334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6035</v>
+        <v>-0.5896</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001</v>
+        <v>-0.8616</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6024</v>
+        <v>0.2721</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6035</v>
+        <v>-0.66</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001</v>
+        <v>-0.66</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6024</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.2016</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.2721</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6696</v>
+        <v>0.136</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3604</v>
+        <v>0.2097</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3092</v>
+        <v>-0.0737</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5437</v>
+        <v>0.3373</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8692</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E. MAÑES CARRETERO</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1185,73 +1185,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5107</v>
+        <v>-0.3846</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2137</v>
+        <v>-1.6175</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2969</v>
+        <v>1.233</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.867</v>
+        <v>-2.0283</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0316</v>
+        <v>0.8116</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1646</v>
+        <v>-2.8399</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5231</v>
+        <v>-0.5937</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2419</v>
+        <v>2.0066</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2811</v>
+        <v>-2.6003</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3901</v>
+        <v>-1.4346</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2736</v>
+        <v>-1.195</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1165</v>
+        <v>-0.2396</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3806</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1984</v>
+        <v>-2.1822</v>
       </c>
       <c r="R10" t="n">
-        <v>2.579</v>
+        <v>1.9838</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0242</v>
+        <v>1.1676</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5384</v>
+        <v>0.2892</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4858</v>
+        <v>0.8784</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1263,73 +1263,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5107</v>
+        <v>-0.7453</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2137</v>
+        <v>1.4608</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2969</v>
+        <v>-2.2061</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.867</v>
+        <v>0.9958</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0316</v>
+        <v>-1.5072</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1646</v>
+        <v>2.503</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5231</v>
+        <v>3.6466</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2419</v>
+        <v>1.0335</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2811</v>
+        <v>2.6131</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3901</v>
+        <v>-2.6508</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2736</v>
+        <v>-2.5408</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1165</v>
+        <v>-0.11</v>
       </c>
       <c r="P11" t="n">
+        <v>-0.7935</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-3.1741</v>
+      </c>
+      <c r="R11" t="n">
         <v>2.3806</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-0.1984</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.579</v>
-      </c>
       <c r="S11" t="n">
-        <v>-1.0242</v>
+        <v>-0.0071</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5384</v>
+        <v>0.1191</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4858</v>
+        <v>-0.1262</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1341,73 +1341,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1684</v>
+        <v>-1.5404</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2341</v>
+        <v>-2.151</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4025</v>
+        <v>0.6106</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9958</v>
+        <v>-1.0076</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5072</v>
+        <v>-0.615</v>
       </c>
       <c r="I12" t="n">
-        <v>2.503</v>
+        <v>-0.3926</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6466</v>
+        <v>0.3712</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0335</v>
+        <v>-0.156</v>
       </c>
       <c r="L12" t="n">
-        <v>2.6131</v>
+        <v>0.5272</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6508</v>
+        <v>-1.3788</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.5408</v>
+        <v>-0.459</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.11</v>
+        <v>-0.9198</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1741</v>
+        <v>-2.1822</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4302</v>
+        <v>0.0623</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1076</v>
+        <v>-0.34</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3226</v>
+        <v>0.4024</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1419,67 +1419,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2353</v>
+        <v>-1.6318</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6215</v>
+        <v>-1.5107</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3862</v>
+        <v>-0.1211</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0076</v>
+        <v>0.6035</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.615</v>
+        <v>0.001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3926</v>
+        <v>0.6024</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3712</v>
+        <v>0.6035</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.156</v>
+        <v>0.001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5272</v>
+        <v>0.6024</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3788</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.459</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9198</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5952</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6326000000000001</v>
+        <v>1.2923</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8105</v>
+        <v>0.5442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1779</v>
+        <v>0.7481</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.5437</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="14">
@@ -1497,16 +1497,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.167299999999999</v>
+        <v>7.2585</v>
       </c>
       <c r="E14" t="n">
-        <v>7.854700000000002</v>
+        <v>9.356800000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6873</v>
+        <v>-2.098</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.6201</v>
+        <v>-2.620100000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-8.1288</v>
@@ -1530,7 +1530,7 @@
         <v>-17.297</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6016999999999999</v>
+        <v>-0.6016999999999998</v>
       </c>
       <c r="P14" t="n">
         <v>7.3401</v>
@@ -1542,16 +1542,16 @@
         <v>19.4416</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0321999999999999</v>
+        <v>2.0588</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5376999999999997</v>
+        <v>0.9642999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5052999999999999</v>
+        <v>1.0945</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4797999999999997</v>
+        <v>0.4798000000000002</v>
       </c>
       <c r="W14" t="n">
         <v>5.2153</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.437</v>
+        <v>2.6828</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8684</v>
+        <v>3.9501</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4314</v>
+        <v>-1.2673</v>
       </c>
       <c r="G15" t="n">
         <v>2.9251</v>
@@ -1620,13 +1620,13 @@
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7022</v>
+        <v>0.948</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5418</v>
+        <v>0.6236</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1603</v>
+        <v>0.3244</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7569</v>
+        <v>0.9431</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4959</v>
+        <v>0.5979</v>
       </c>
       <c r="F16" t="n">
-        <v>0.261</v>
+        <v>0.3452</v>
       </c>
       <c r="G16" t="n">
         <v>0.8254</v>
@@ -1698,13 +1698,13 @@
         <v>0.1984</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.267</v>
+        <v>-0.0808</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.187</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0799</v>
+        <v>0.0042</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1719,7 +1719,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1731,64 +1731,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3853</v>
+        <v>0.9011</v>
       </c>
       <c r="E17" t="n">
-        <v>0.139</v>
+        <v>1.678</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2463</v>
+        <v>-0.7769</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4003</v>
+        <v>-1.6999</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2101</v>
+        <v>0.7307</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6104</v>
+        <v>-2.4306</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4463</v>
+        <v>0.7986</v>
       </c>
       <c r="K17" t="n">
-        <v>0.121</v>
+        <v>1.7848</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3253</v>
+        <v>-0.9862</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.046</v>
+        <v>-2.4985</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3311</v>
+        <v>-1.0541</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2851</v>
+        <v>-1.4444</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3968</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R17" t="n">
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4874</v>
+        <v>0.18</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1926</v>
+        <v>0.0454</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2948</v>
+        <v>0.1345</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8692</v>
+        <v>3.0162</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8692</v>
+        <v>3.0162</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1797,7 +1797,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. POU BLINNIKOV</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1809,73 +1809,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3168</v>
+        <v>0.5979</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9211</v>
+        <v>-0.065</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6043</v>
+        <v>0.6629</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0885</v>
+        <v>0.4003</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4739</v>
+        <v>-1.2101</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5624</v>
+        <v>1.6104</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4117</v>
+        <v>1.4463</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9312</v>
+        <v>0.121</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5195</v>
+        <v>1.3253</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5002</v>
+        <v>-1.046</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4573</v>
+        <v>-1.3311</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0428</v>
+        <v>0.2851</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1903</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.051</v>
+        <v>-0.2749</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1758</v>
+        <v>-0.3967</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2268</v>
+        <v>0.1218</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>0.8692</v>
       </c>
       <c r="W18" t="n">
-        <v>0.532</v>
+        <v>0.8692</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>A. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1887,73 +1887,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0701</v>
+        <v>0.4189</v>
       </c>
       <c r="E19" t="n">
-        <v>1.159</v>
+        <v>1.615</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2291</v>
+        <v>-1.1962</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6764</v>
+        <v>-1.0885</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4688</v>
+        <v>0.4739</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1452</v>
+        <v>-1.5624</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1549</v>
+        <v>1.4117</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9917</v>
+        <v>1.9312</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1632</v>
+        <v>-0.5195</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8313</v>
+        <v>-2.5002</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5229</v>
+        <v>-1.4573</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3084</v>
+        <v>-1.0428</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1741</v>
+        <v>-0.1984</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5982</v>
+        <v>0.051</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0431</v>
+        <v>-0.1303</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5551</v>
+        <v>0.1813</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1352</v>
+        <v>0.532</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7384</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5979</v>
+        <v>-0.3554</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7597</v>
+        <v>-0.6091</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3576</v>
+        <v>0.2538</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6999</v>
+        <v>0.6691</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7307</v>
+        <v>-1.0889</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4306</v>
+        <v>1.7581</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7986</v>
+        <v>0.9103</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7848</v>
+        <v>-0.2971</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9862</v>
+        <v>1.2074</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4985</v>
+        <v>-0.2412</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0541</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4444</v>
+        <v>0.5507</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.319</v>
+        <v>-0.6872</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8728</v>
+        <v>-0.7935</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4462</v>
+        <v>0.1062</v>
       </c>
       <c r="V20" t="n">
-        <v>3.0162</v>
+        <v>-0.3373</v>
       </c>
       <c r="W20" t="n">
-        <v>3.0162</v>
+        <v>0.266</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,67 +2043,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9157</v>
+        <v>-1.2059</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8132</v>
+        <v>0.6489</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1025</v>
+        <v>-1.8548</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6691</v>
+        <v>-0.6764</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0889</v>
+        <v>0.4688</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7581</v>
+        <v>-1.1452</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9103</v>
+        <v>2.1549</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2971</v>
+        <v>1.9917</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2074</v>
+        <v>0.1632</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2412</v>
+        <v>-2.8313</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-1.5229</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5507</v>
+        <v>-1.3084</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2475</v>
+        <v>1.4623</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.5329</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.25</v>
+        <v>0.9294</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3373</v>
+        <v>-0.6032</v>
       </c>
       <c r="W21" t="n">
-        <v>0.266</v>
+        <v>1.1352</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6032</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="22">
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7327</v>
+        <v>-1.6111</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7669</v>
+        <v>-2.6648</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0342</v>
+        <v>1.0537</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1247</v>
@@ -2166,13 +2166,13 @@
         <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7352</v>
+        <v>-0.6136</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7481</v>
+        <v>-0.6461</v>
       </c>
       <c r="U22" t="n">
-        <v>0.013</v>
+        <v>0.0325</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6745</v>
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7652</v>
+        <v>-2.8613</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2256</v>
+        <v>-1.4296</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5396</v>
+        <v>-1.4316</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0219</v>
@@ -2244,13 +2244,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.132</v>
+        <v>-0.2281</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1926</v>
+        <v>-0.3967</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0606</v>
+        <v>0.1686</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8097</v>
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4925</v>
+        <v>-3.1474</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1472</v>
+        <v>-1.331</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3452</v>
+        <v>-1.8164</v>
       </c>
       <c r="G24" t="n">
         <v>0.5445</v>
@@ -2322,13 +2322,13 @@
         <v>1.3887</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0531</v>
+        <v>0.2919</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5611</v>
+        <v>0.2551</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.492</v>
+        <v>0.0368</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2065</v>
@@ -2355,16 +2355,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6781</v>
+        <v>-3.6373</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3902</v>
+        <v>2.3904</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.068200000000001</v>
+        <v>-6.0276</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.7530000000000003</v>
       </c>
       <c r="H25" t="n">
         <v>6.0972</v>
@@ -2379,7 +2379,7 @@
         <v>15.0235</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4851000000000003</v>
+        <v>0.4851000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-14.7554</v>
@@ -2400,16 +2400,16 @@
         <v>11.9031</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9917999999999999</v>
+        <v>1.0486</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9910000000000001</v>
+        <v>-0.9913</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0007000000000000339</v>
+        <v>2.0397</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.4797999999999996</v>
+        <v>-0.4798</v>
       </c>
       <c r="W25" t="n">
         <v>4.7356</v>
